--- a/processed_ruby_restored_xlsx/sc233_凛５：二段ベッド足扱き.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc233_凛５：二段ベッド足扱き.ss.xlsx
@@ -606,7 +606,8 @@
       <c r="B10" s="1" t="inlineStr">
         <is>
           <t>I hooked my foot on the ladder and peered up, and
-Miru-chan had her shoulders slumped in disappointment.</t>
+Miru-chan had her shoulders slumped in
+disappointment.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -804,7 +805,8 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Celebrity Mode is, so to speak, an insanely hard mode.</t>
+          <t>Celebrity Mode is, so to speak, an insanely hard
+mode.</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -835,8 +837,8 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>If you miss, the whole rhythm falls apart at once, and
-it's extremely difficult to recover — it's a very
+          <t>If you miss, the whole rhythm falls apart at once,
+and it's extremely difficult to recover — it's a very
 high-difficulty mode.</t>
         </is>
       </c>
@@ -943,8 +945,8 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>I snort proudly, but Miru-chan looks back at me with a
-puzzled expression.</t>
+          <t>I snort proudly, but Miru-chan looks back at me with
+a puzzled expression.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -959,8 +961,8 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Still, I’m confident this is one thing I won’t lose to
-anyone, so you can look forward to it！</t>
+          <t>Still, I’m confident this is one thing I won’t lose
+to anyone, so you can look forward to it！</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1663,8 +1665,8 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>But since I've already started, I can't let myself get
-distracted.</t>
+          <t>But since I've already started, I can't let myself
+get distracted.</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1679,8 +1681,8 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>This celebrity mode is exactly the kind of thing where
-a single slip-up can be fatal….</t>
+          <t>This celebrity mode is exactly the kind of thing
+where a single slip-up can be fatal….</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2349,9 +2351,9 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>She seems to be parroting me, but since she even tried
-Celebrity Mode, she probably actually gets it more
-than she lets on.</t>
+          <t>She seems to be parroting me, but since she even
+tried Celebrity Mode, she probably actually gets it
+more than she lets on.</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3804,8 +3806,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>I’m of course worried about down there too, so instead
-of crying out I let out a short breath.</t>
+          <t>I’m of course worried about down there too, so
+instead of crying out I let out a short breath.</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -4020,8 +4022,8 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>There's no way I can say I feel like my penis is being
-toyed with.</t>
+          <t>There's no way I can say I feel like my penis is
+being toyed with.</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4232,8 +4234,8 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan is about the game, and Rin-chan is about the
-penis...</t>
+          <t>Miru-chan is about the game, and Rin-chan is about
+the penis...</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4248,7 +4250,8 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>There's no way I can neatly separate those thoughts...</t>
+          <t>There's no way I can neatly separate those
+thoughts...</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4569,8 +4572,8 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Matching Rin-chan's words, the stimulation to my penis
-shifts shape.</t>
+          <t>Matching Rin-chan's words, the stimulation to my
+penis shifts shape.</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4585,8 +4588,8 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>It's not just being pressed against—it feels like it's
-being sandwiched.</t>
+          <t>It's not just being pressed against—it feels like
+it's being sandwiched.</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4891,8 +4894,8 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>「Whoa~! I never thought of doing it with legs. Ton-ton
-it is then!」</t>
+          <t>「Whoa~! I never thought of doing it with legs.
+Ton-ton it is then!」</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4922,8 +4925,8 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>But... oh god！ At this point I just want anyone to fix
-this situation...！</t>
+          <t>But... oh god！ At this point I just want anyone to
+fix this situation...！</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5061,8 +5064,9 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>In other words, the right mix of firmness and softness
-stimulates the penis, making it twitch and pulse…！</t>
+          <t>In other words, the right mix of firmness and
+softness stimulates the penis, making it twitch and
+pulse…！</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5538,8 +5542,8 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>This is a whole new kind of stimulation... could it be
-they're doing it with their toes？</t>
+          <t>This is a whole new kind of stimulation... could it
+be they're doing it with their toes？</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5693,8 +5697,8 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh, Miru-chan！ Th-this is… haaah, ngg！ I’m keeping
-the rhythm with my mouth…！」</t>
+          <t>「Aahhh, Miru-chan！ Th-this is… haaah, ngg！ I’m
+keeping the rhythm with my mouth…！」</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5755,8 +5759,8 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>The awkward movements of the feet gradually settled in
-and started giving even more stimulation.</t>
+          <t>The awkward movements of the feet gradually settled
+in and started giving even more stimulation.</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5985,8 +5989,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>Aah！ I couldn't help letting out a loud sound right in
-front of Miru-chan...！</t>
+          <t>Aah！ I couldn't help letting out a loud sound right
+in front of Miru-chan...！</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6078,8 +6082,8 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>But oddly, my senses sharpened, and sheer momentum was
-keeping me afloat.</t>
+          <t>But oddly, my senses sharpened, and sheer momentum
+was keeping me afloat.</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -6125,8 +6129,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>Maybe having figured it out, Rin-chan's foot movements
-no longer stopped.</t>
+          <t>Maybe having figured it out, Rin-chan's foot
+movements no longer stopped.</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6157,8 +6161,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>When she rubbed it even more, pleasure spilled out and
-I felt like I was about to explode...！</t>
+          <t>When she rubbed it even more, pleasure spilled out
+and I felt like I was about to explode...！</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6437,8 +6441,8 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>My legs started trembling, and it feels like I’m going
-to slip and tumble down the stairs.</t>
+          <t>My legs started trembling, and it feels like I’m
+going to slip and tumble down the stairs.</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -6896,9 +6900,9 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>To take my mind off the pleasure of ejaculating, I let
-out a triumphant shout from the excitement of clearing
-the game.</t>
+          <t>To take my mind off the pleasure of ejaculating, I
+let out a triumphant shout from the excitement of
+clearing the game.</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -7221,8 +7225,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ahaha！ If you do it while shouting like this, you
-can clear Celebrity Mode too！」</t>
+          <t>「Ah, ahaha！ If you do it while shouting like this,
+you can clear Celebrity Mode too！」</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7332,8 +7336,8 @@
       <c r="B448" s="1" t="inlineStr">
         <is>
           <t>When I quietly switched off the game console, the
-HimePara music that had been blasting suddenly quieted
-down.</t>
+HimePara music that had been blasting suddenly
+quieted down.</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -7500,8 +7504,8 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Rin, listen, listen~！ Onii-chan cleared Celebrity
-Mode！」</t>
+          <t>「Ah！ Rin, listen, listen~！ Onii-chan cleared
+Celebrity Mode！」</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7927,8 +7931,8 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>「Eeeh！ That's not fair！ No fair！ You have to tell Miru
-too！」</t>
+          <t>「Eeeh！ That's not fair！ No fair！ You have to tell
+Miru too！」</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -8019,7 +8023,8 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Niini, you've 100%-completed HimePara, right！？」</t>
+          <t>「Ah... Niini, you've 100%-completed HimePara,
+right！？」</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8140,8 +8145,8 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>I managed to steer Miru-chan just right and got her to
-focus on the game.</t>
+          <t>I managed to steer Miru-chan just right and got her
+to focus on the game.</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8246,9 +8251,9 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>Now that you mention it, my underwear’s been left down
-and I haven’t had them put back on, and we’ve got a
-mountain of problems！</t>
+          <t>Now that you mention it, my underwear’s been left
+down and I haven’t had them put back on, and we’ve
+got a mountain of problems！</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8293,8 +8298,8 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>I wink at Rin-chan over and over and send signals with
-my eyes so Miru-chan can’t see.</t>
+          <t>I wink at Rin-chan over and over and send signals
+with my eyes so Miru-chan can’t see.</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8401,7 +8406,8 @@
       <c r="B518" s="1" t="inlineStr">
         <is>
           <t>Even if we tried to signal each other secretly, it
-wasn't like Miru-chan nearby wouldn't notice at all...</t>
+wasn't like Miru-chan nearby wouldn't notice at
+all...</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8584,8 +8590,8 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>For now, I think I should direct Miru-chan's attention
-to the game, so I start playing.</t>
+          <t>For now, I think I should direct Miru-chan's
+attention to the game, so I start playing.</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8828,8 +8834,8 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Hahahaah！ If you do it like this...！ You can make
-the whole clit cum！」</t>
+          <t>「Ah！ Hahahaah！ If you do it like this...！ You can
+make the whole clit cum！」</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -8890,7 +8896,8 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>「...Mi-Miru, maybe it's okay if you can't clear it...」</t>
+          <t>「...Mi-Miru, maybe it's okay if you can't clear
+it...」</t>
         </is>
       </c>
       <c r="C550" t="n">

--- a/processed_ruby_restored_xlsx/sc233_凛５：二段ベッド足扱き.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc233_凛５：二段ベッド足扱き.ss.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>「I know that, but... they're a celeb, you know~~？」</t>
+          <t>I know that, but... they're a celeb, you know~~？</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru-chan</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Muruku</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Muruku</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>「Hey hey, Onii-chan？ Where is this~？」</t>
+          <t>Hey hey, Onii-chan？ Where is this~？</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3606,8 +3606,8 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>「Ah, huh？ Oh… here you just keep mashing it and it'll
-be fine…」</t>
+          <t>Ah, huh？ Oh… here you just keep mashing it and it」ll
+be fine…</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>「Woooaaah~！ Amazing, thirty perfect hits in a row！」</t>
+          <t>Woooaaah~！ Amazing, thirty perfect hits in a row！</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>「Mm, ah… yeah.」</t>
+          <t>Mm, ah… yeah.</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>「Phew…」</t>
+          <t>Phew…</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>「Heeey！　Onii-chan？」</t>
+          <t>Heeey！　Onii-chan？</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>「Whoa！？」</t>
+          <t>Whoa！？</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ What's wrong？」</t>
+          <t>Huh？ What」s wrong？</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>「Ah… haha. No, no, it's nothing.」</t>
+          <t>Ah… haha. No, no, it」s nothing.</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Aaaah... what the hell is happening！</t>
+          <t>Aaaah... what the hell is happening！"</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>...Did I somehow manage to talk her into it？</t>
+          <t>...Did I somehow manage to talk them into it？</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Onii-chan, help！」</t>
+          <t>Ah！ Onii-chan, help！</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5278,8 +5278,8 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>Even though I'm flustered, I judge from experience
-that I can still turn it around.</t>
+          <t>Even though he's flustered, he judges from experience
+that he can still turn it around.</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5294,9 +5294,9 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>Even so, with Rin-chan slowly teasing my penis with
-her feet, I also start to feel like Miru-chan is
-verbally tormenting me.</t>
+          <t>Even so, with Rin-chan slowly teasing his penis with
+her feet, he also starts to feel like Miru-chan is
+verbally tormenting him.</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>「Nn！　Nn—...」</t>
+          <t>Nn！　Nn—...</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5775,8 +5775,8 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>I start to wonder if I'm a masochist, because this
-feels so damn good.</t>
+          <t>She starts to wonder if she's a masochist, because
+this feels so damn good.</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -6379,8 +6379,8 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>「Aaaahhh！ Come on！ It's just a little more... Ah,
-yeah！ Right now — this is the good part...！」</t>
+          <t>Aaaahhh！ Come on！ It's just a little more... Ah,
+yeah！ Right now — this is the good part...！</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6854,8 +6854,8 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>At the same time the tension in my penis drains away,
-and I come hard…！</t>
+          <t>At the same time the tension in his penis drains
+away, and he comes hard…！</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>「Uuuaaah！　Yesss！　Oh！　Ooooh！　Oooaaah！」</t>
+          <t>Uuuaaah！　Yesss！　Oh！　Ooooh！　Oooaaah！</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>「Yeah… I'm here？」</t>
+          <t>Yeah… I」m here？</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>「Mmm~~~~~？　Ah！　Mm-hmm！」</t>
+          <t>Mmm~~~~~？　Ah！　Mm-hmm！</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8653,7 +8653,7 @@
       <c r="B534" s="1" t="inlineStr">
         <is>
           <t>I'll have Rin-chan do the bare minimum in this gap...
-whoa—！？</t>
+whoa—！？"</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>And then—Rin-chan's moouuuth!？!</t>
+          <t>And then—Rin-chan's moouuuth!？!"</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>「Ofuuooo！？」</t>
+          <t>Ofuuooo！？</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>「Hii！？　Onii-chan...？」</t>
+          <t>Hii！？　Onii-chan...？</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>Because, what else am I supposed to do...！？</t>
+          <t>Because, what else am I supposed to do...！？"</t>
         </is>
       </c>
       <c r="C548" t="n">
